--- a/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -452,84 +452,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>number estimates</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Pooled RR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>lower CI RR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>upper CI RR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lower PI RR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>upper PI RR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>I^2 (%)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>eggers p-value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>total N</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>total Cases</t>
-        </is>
+      <c r="A1" s="1" t="str">
+        <v>Exposure</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <v>number estimates</v>
+      </c>
+      <c r="C1" s="1" t="str">
+        <v>Pooled RR</v>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v>lower CI RR</v>
+      </c>
+      <c r="E1" s="1" t="str">
+        <v>upper CI RR</v>
+      </c>
+      <c r="F1" s="1" t="str">
+        <v>lower PI RR</v>
+      </c>
+      <c r="G1" s="1" t="str">
+        <v>upper PI RR</v>
+      </c>
+      <c r="H1" s="1" t="str">
+        <v>I^2 (%)</v>
+      </c>
+      <c r="I1" s="1" t="str">
+        <v>eggers p-value</v>
+      </c>
+      <c r="J1" s="1" t="str">
+        <v>total N</v>
+      </c>
+      <c r="K1" s="1" t="str">
+        <v>total Cases</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>alpha_linolenic_acid</t>
-        </is>
+      <c r="A2" t="str">
+        <v>alpha_linolenic_acid</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2608764404894685</v>
+        <v>0.260876440489468</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1004102763893268</v>
+        <v>0.100410276389327</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.6510344938106651</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+        <v>0.651034493810665</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>561</v>
       </c>
@@ -538,27 +514,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A3" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2608764404894685</v>
+        <v>0.260876440489468</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1004102763893268</v>
+        <v>0.100410276389327</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.6510344938106651</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+        <v>0.651034493810665</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>561</v>
       </c>
@@ -567,27 +541,25 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A4" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2608764404894685</v>
+        <v>0.260876440489468</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1004102763893268</v>
+        <v>0.100410276389327</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.6510344938106651</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+        <v>0.651034493810665</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>561</v>
       </c>
@@ -596,27 +568,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>multivitamin</t>
-        </is>
+      <c r="A5" t="str">
+        <v>multivitamin</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.3910830654414335</v>
+        <v>0.391083065441434</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2408309631552709</v>
+        <v>0.240830963155271</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.6310600546798513</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+        <v>0.631060054679851</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>667</v>
       </c>
@@ -625,27 +595,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A6" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.4311156410559245</v>
+        <v>0.431115641055925</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.9601743676651679</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+        <v>0.960174367665168</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>561</v>
       </c>
@@ -654,27 +622,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A7" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.4311156410559245</v>
+        <v>0.431115641055925</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.9601743676651679</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+        <v>0.960174367665168</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>561</v>
       </c>
@@ -683,27 +649,25 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>olive</t>
-        </is>
+      <c r="A8" t="str">
+        <v>olive</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.4711336417688241</v>
+        <v>0.471133641768824</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.2809182656266805</v>
+        <v>0.28091826562668</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.7807798429070956</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+        <v>0.780779842907096</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>586</v>
       </c>
@@ -712,27 +676,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>olive_oil_intake</t>
-        </is>
+      <c r="A9" t="str">
+        <v>olive_oil_intake</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.4711336417688241</v>
+        <v>0.471133641768824</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2809182656266805</v>
+        <v>0.28091826562668</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.7807798429070956</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+        <v>0.780779842907096</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>586</v>
       </c>
@@ -741,27 +703,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A10" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.5611208951000519</v>
+        <v>0.561120895100052</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.3109741576462426</v>
+        <v>0.310974157646243</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.019907392408769</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>561</v>
       </c>
@@ -770,27 +730,25 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A11" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.5811080568427878</v>
+        <v>0.581108056842788</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.3109741576462426</v>
+        <v>0.310974157646243</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.059711334632446</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="2" t="n">
         <v>561</v>
       </c>
@@ -799,29 +757,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>legumes</t>
-        </is>
+      <c r="A12" t="str">
+        <v>legumes</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.6397997770084459</v>
+        <v>0.639799777008446</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.4305034246903502</v>
+        <v>0.43050342469035</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.9507539286723269</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+        <v>0.950753928672327</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="4" t="n">
         <v>77.91</v>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>2541</v>
       </c>
@@ -830,29 +786,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A13" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.6435857533404954</v>
+        <v>0.643585753340495</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.2494242542659014</v>
+        <v>0.249424254265901</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1.660634901453039</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>70.34</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>101981</v>
       </c>
@@ -861,34 +815,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>whole_grain_intake</t>
-        </is>
+      <c r="A14" t="str">
+        <v>whole_grain_intake</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.7226718735643111</v>
+        <v>0.722671873564311</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.5177307290339085</v>
+        <v>0.517730729033908</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1.008737954989623</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.01658634469437209</v>
+        <v>0.016586344693104</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>31.48702420360033</v>
+        <v>31.487024206007852</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>75.47</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.2822678427106021</v>
+        <v>0.282267842710602</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>219042</v>
@@ -898,34 +850,32 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A15" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.7311036772103915</v>
+        <v>0.731103677210392</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.5091055075111857</v>
+        <v>0.509105507511186</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1.049905331889996</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1542791183442667</v>
+        <v>0.154279118347241</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3.4645815491233</v>
+        <v>3.464581549056503</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>72.20999999999999</v>
+        <v>72.21</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.1116807897528627</v>
+        <v>0.111680789752863</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>307597</v>
@@ -935,34 +885,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A16" t="str">
+        <v>dairy</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.7336670233195703</v>
+        <v>0.73366702331957</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.5325385444896668</v>
+        <v>0.532538544489667</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1.010757449721169</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2667027912984513</v>
+        <v>0.266702791298452</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.018228974980078</v>
+        <v>2.01822897498007</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>80.88</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.03414991977459563</v>
+        <v>0.034149919774596</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>306953</v>
@@ -972,34 +920,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fermented_foods</t>
-        </is>
+      <c r="A17" t="str">
+        <v>fermented_foods</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.7490122054026693</v>
+        <v>0.749012205402669</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.5024294735717695</v>
+        <v>0.50242947357177</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>1.116613004117546</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1999700203677981</v>
+        <v>0.199970020367752</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2.805516961043995</v>
+        <v>2.805516961044641</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>73.37</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.6646008321307554</v>
+        <v>0.664600832130755</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>203999</v>
@@ -1009,27 +955,25 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>non_nutritive_sweetener_intake</t>
-        </is>
+      <c r="A18" t="str">
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.7504264322028401</v>
+        <v>0.75042643220284</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.5305667184532947</v>
+        <v>0.530566718453295</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1.059855422172594</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>80388</v>
       </c>
@@ -1038,34 +982,32 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A19" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.7509621709935039</v>
+        <v>0.750962170993504</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.5556037048097945</v>
+        <v>0.555603704809794</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1.014910062303704</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.05110412975560341</v>
+        <v>0.051104129752821</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11.03519783939657</v>
+        <v>11.035197839997357</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>26.75</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.7498815991687291</v>
+        <v>0.749881599168729</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>8606</v>
@@ -1075,29 +1017,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.7692032808507674</v>
+        <v>0.769203280850767</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.3929393518554822</v>
+        <v>0.392939351855482</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.505612812937899</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+        <v>1.505612812937898</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
-        <v>73.15000000000001</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
+        <v>73.15</v>
+      </c>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>121519</v>
       </c>
@@ -1106,27 +1046,25 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
+      <c r="A21" t="str">
+        <v>vitamin_b12</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.7708048744499005</v>
+        <v>0.7708048744499</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.6110819817568988</v>
+        <v>0.611081981756899</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0.990044948040641</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>2589</v>
       </c>
@@ -1135,29 +1073,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>avocado</t>
-        </is>
+      <c r="A22" t="str">
+        <v>avocado</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.7773224664291063</v>
+        <v>0.777322466429106</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.5959491108750986</v>
+        <v>0.595949110875099</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1.013794275030678</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>112328</v>
       </c>
@@ -1166,27 +1102,25 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A23" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.8303208655186842</v>
+        <v>0.830320865518684</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.6705029098644103</v>
+        <v>0.67050290986441</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>1.029929753803904</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="2" t="n">
         <v>101721</v>
       </c>
@@ -1195,29 +1129,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A24" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.8387018493286374</v>
+        <v>0.838701849328638</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.7048290414313586</v>
+        <v>0.704829041431359</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.9981018038573761</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
+        <v>0.998101803857376</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="4" t="n">
         <v>38.28</v>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1226,29 +1158,27 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A25" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.8530816628701524</v>
+        <v>0.853081662870152</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.7636085425406669</v>
+        <v>0.763608542540667</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.9529431793814942</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+        <v>0.952943179381494</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="2" t="n">
         <v>676447</v>
       </c>
@@ -1257,137 +1187,129 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>soluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A26" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="n">
+        <v>0.859761718188435</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.737639541391075</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1.002002001334</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.518575557319163</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1.425424321739458</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0.120413157123371</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>881889</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>8536</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>soluble_dietary_fiber_intake</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.86027378065949</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0.6804949413246006</v>
-      </c>
-      <c r="E26" s="3" t="n">
+      <c r="D27" s="3" t="n">
+        <v>0.680494941324601</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>1.079803598340883</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="2" t="n">
         <v>101721</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K27" s="2" t="n">
         <v>776</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
+    <row r="28">
+      <c r="A28" t="str">
+        <v>vitamin_e</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>0.8602777300074131</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0.6890785559681998</v>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="C28" s="3" t="n">
+        <v>0.860277730007413</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.6890785559682</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>1.074010744256656</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>0.5285804357154186</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>1.400123278768412</v>
-      </c>
-      <c r="H27" s="4" t="n">
+      <c r="F28" s="3" t="n">
+        <v>0.528580435718609</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1.400123278759961</v>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>0.6162620179384339</v>
-      </c>
-      <c r="J27" s="2" t="n">
+      <c r="I28" s="5" t="n">
+        <v>0.616262017938434</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>157524</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K28" s="2" t="n">
         <v>1453</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0.8820557644270329</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0.7588888158485086</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1.025212594138781</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.5369416697280761</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>1.448988624691713</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>85.17</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>0.194272186346288</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>1002741</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>9130</v>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A29" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.8823204208528399</v>
+        <v>0.88232042085284</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.7072295387051121</v>
+        <v>0.707229538705112</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.100648993591191</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4501580331890584</v>
+        <v>0.450158033189006</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.72936894969723</v>
+        <v>1.729368949697432</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>54.04</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.7000669639927898</v>
+        <v>0.70006696399279</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>366541</v>
@@ -1397,27 +1319,25 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mediterranean_diet</t>
-        </is>
+      <c r="A30" t="str">
+        <v>mediterranean_diet</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.8902226072035401</v>
+        <v>0.89022260720354</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.6205359319277568</v>
+        <v>0.620535931927757</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1.259255513560131</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>37442</v>
       </c>
@@ -1426,16 +1346,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A31" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.9462958698523343</v>
+        <v>0.946295869852334</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0.436660182850176</v>
@@ -1443,12 +1361,12 @@
       <c r="E31" s="3" t="n">
         <v>2.050943641160259</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="4" t="n">
         <v>88.7</v>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>648914</v>
       </c>
@@ -1457,25 +1375,23 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A32" t="str">
+        <v>tea</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.9617507091463667</v>
+        <v>0.961750709146367</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7890701910914995</v>
+        <v>0.7890701910915</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1.172337946680718</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5117552101281551</v>
+        <v>0.511755210128155</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>1.807435289836927</v>
@@ -1484,7 +1400,7 @@
         <v>83.53</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.02398376617759525</v>
+        <v>0.023983766177595</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>580076</v>
@@ -1494,29 +1410,27 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>phosphorus</t>
-        </is>
+      <c r="A33" t="str">
+        <v>phosphorus</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.9740428329225616</v>
+        <v>0.974042832922562</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.2712267749764213</v>
+        <v>0.271226774976421</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>3.498030164795818</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="4" t="n">
-        <v>82.45999999999999</v>
-      </c>
-      <c r="I33" s="5" t="inlineStr"/>
+        <v>82.46</v>
+      </c>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>1147</v>
       </c>
@@ -1525,10 +1439,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A34" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
@@ -1537,22 +1449,22 @@
         <v>1.026135700809198</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.8760781322122511</v>
+        <v>0.876078132212251</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.201895627523871</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.1861215877235062</v>
+        <v>0.186121587717069</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5.657347378958563</v>
+        <v>5.657347379154214</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>71.67</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.6179812083215527</v>
+        <v>0.617981208321553</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>575001</v>
@@ -1562,10 +1474,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
+      <c r="A35" t="str">
+        <v>iron</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1574,15 +1484,15 @@
         <v>1.049880653285851</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.9900225074278087</v>
+        <v>0.990022507427809</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>1.119694504834913</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>481419</v>
       </c>
@@ -1591,10 +1501,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A36" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>2</v>
@@ -1603,17 +1511,17 @@
         <v>1.053375742513365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.8658011636136935</v>
+        <v>0.865801163613694</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.281588084594754</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>222535</v>
       </c>
@@ -1622,10 +1530,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>7</v>
@@ -1634,13 +1540,13 @@
         <v>1.086433159799911</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.9792189645694596</v>
+        <v>0.97921896456946</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>1.205265651112213</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.8385628597437634</v>
+        <v>0.838562859743763</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>1.407571295339136</v>
@@ -1649,7 +1555,7 @@
         <v>41.47</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.08383782424174292</v>
+        <v>0.083837824241743</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>938913</v>
@@ -1659,10 +1565,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>western_pattern_diet</t>
-        </is>
+      <c r="A38" t="str">
+        <v>western_pattern_diet</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1676,10 +1580,10 @@
       <c r="E38" s="3" t="n">
         <v>1.378808493040073</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>388077</v>
       </c>
@@ -1688,10 +1592,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A39" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -1705,10 +1607,10 @@
       <c r="E39" s="3" t="n">
         <v>1.219390011363415</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>73024</v>
       </c>
@@ -1717,10 +1619,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A40" t="str">
+        <v>lutein</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1734,10 +1634,10 @@
       <c r="E40" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1746,10 +1646,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A41" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1763,12 +1661,12 @@
       <c r="E41" s="3" t="n">
         <v>1.233678059956743</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1777,10 +1675,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A42" t="str">
+        <v>selenium</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1789,15 +1685,15 @@
         <v>1.129666097028344</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.7004776402833592</v>
+        <v>0.700477640283359</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>1.836490637351607</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>34887</v>
       </c>
@@ -1806,10 +1702,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A43" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>2</v>
@@ -1823,12 +1717,12 @@
       <c r="E43" s="3" t="n">
         <v>1.277365814492968</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1837,10 +1731,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A44" t="str">
+        <v>tomato</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1849,15 +1741,15 @@
         <v>1.19945453907786</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.9501079967336835</v>
+        <v>0.950107996733684</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1.518204486493061</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>101683</v>
       </c>
@@ -1866,10 +1758,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A45" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>9</v>
@@ -1884,16 +1774,16 @@
         <v>1.570980583701342</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.7815874035063086</v>
+        <v>0.781587403506308</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.234524144537296</v>
+        <v>2.234524144537297</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>77.01000000000001</v>
+        <v>77.01</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.01127626650555045</v>
+        <v>0.01127626650555</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1417360</v>
@@ -1903,188 +1793,172 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>soy</t>
-        </is>
+      <c r="A46" t="str">
+        <v>calcium</v>
       </c>
       <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1.763833989140762</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3.119550071749652</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>caffeine</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2.045114195119933</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1.149607920243644</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>3.637955664073244</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="2" t="n">
+        <v>104440</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>pickled_vegetables</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3.217136946095633</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.357780842990217</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>7.482070687809</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>vegetable_and_seed_oil_intake</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3.431519625226634</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1.684722438489189</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>6.946365883186642</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>eggs</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>1.508325356558058</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>0.1884919459617998</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>12.0697219694313</v>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
-        <v>32477</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>1.763833989140762</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>3.119550071749652</v>
-      </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
-        <v>586</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>caffeine</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>2.045114195119933</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>1.149607920243644</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>3.637955664073244</v>
-      </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
-        <v>104440</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>3.217136946095633</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>1.357780842990217</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>7.482070687809</v>
-      </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>vegetable_and_seed_oil_intake</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="C50" s="3" t="n">
-        <v>3.431519625226634</v>
+        <v>3.857811292537815</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1.684722438489189</v>
+        <v>2.646928735129925</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>6.946365883186642</v>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
+        <v>5.622632665288498</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5"/>
       <c r="J50" s="2" t="n">
-        <v>405</v>
+        <v>1995</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>113</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A51" t="str">
+        <v>soy</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3.857811292537815</v>
+        <v>4.61</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2.646928735129925</v>
+        <v>1.57</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>5.622632665288498</v>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5" t="inlineStr"/>
+        <v>13.51</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="2" t="n">
-        <v>1995</v>
+        <v>18244</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>355</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A52" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -2096,12 +1970,12 @@
         <v>1.456957290394739</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>20.44949521459941</v>
-      </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
+        <v>20.449495214599413</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="5"/>
       <c r="J52" s="2" t="n">
         <v>199</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="str">
         <v>Exposure</v>
@@ -886,219 +886,219 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>dairy</v>
+        <v>fermented_foods</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.73366702331957</v>
+        <v>0.749012205402669</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.532538544489667</v>
+        <v>0.50242947357177</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.010757449721169</v>
+        <v>1.116613004117546</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.266702791298452</v>
+        <v>0.199970020367752</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.01822897498007</v>
+        <v>2.805516961044641</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>80.88</v>
+        <v>73.37</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.034149919774596</v>
+        <v>0.664600832130755</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>306953</v>
+        <v>203999</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3788</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>fermented_foods</v>
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.749012205402669</v>
+        <v>0.75042643220284</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.50242947357177</v>
+        <v>0.530566718453295</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.116613004117546</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.199970020367752</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>2.805516961044641</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>73.37</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0.664600832130755</v>
-      </c>
+        <v>1.059855422172594</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
-        <v>203999</v>
+        <v>80388</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2474</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>non_nutritive_sweetener_intake</v>
+        <v>vitamin_c</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.75042643220284</v>
+        <v>0.750962170993504</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.530566718453295</v>
+        <v>0.555603704809794</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.059855422172594</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+        <v>1.014910062303704</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.051104129752821</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.035197839997357</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.749881599168729</v>
+      </c>
       <c r="J18" s="2" t="n">
-        <v>80388</v>
+        <v>8606</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>448</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>vitamin_c</v>
+        <v>vitamin_a</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.750962170993504</v>
+        <v>0.769203280850767</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.555603704809794</v>
+        <v>0.392939351855482</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.014910062303704</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.051104129752821</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>11.035197839997357</v>
-      </c>
+        <v>1.505612812937898</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>0.749881599168729</v>
-      </c>
+        <v>73.15</v>
+      </c>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
-        <v>8606</v>
+        <v>121519</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>902</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>vitamin_a</v>
+        <v>vitamin_b12</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.769203280850767</v>
+        <v>0.7708048744499</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.392939351855482</v>
+        <v>0.611081981756899</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.505612812937898</v>
+        <v>0.990044948040641</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="4" t="n">
-        <v>73.15</v>
-      </c>
+      <c r="H20" s="4"/>
       <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
-        <v>121519</v>
+        <v>2589</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>737</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>vitamin_b12</v>
+        <v>avocado</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.7708048744499</v>
+        <v>0.777322466429106</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.611081981756899</v>
+        <v>0.595949110875099</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.990044948040641</v>
+        <v>1.013794275030678</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
+      <c r="H21" s="4" t="n">
+        <v>20.99</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
-        <v>2589</v>
+        <v>112328</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>avocado</v>
+        <v>dairy</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.777322466429106</v>
+        <v>0.8285318499048928</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.595949110875099</v>
+        <v>0.6515507423707737</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.013794275030678</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+        <v>1.0536918026427677</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.3820831459958125</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1.7966378090761093</v>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I22" s="5"/>
+        <v>78.58</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0.13803210241351754</v>
+      </c>
       <c r="J22" s="2" t="n">
-        <v>112328</v>
+        <v>799763</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1165</v>
+        <v>5469</v>
       </c>
     </row>
     <row r="23">
@@ -1531,37 +1531,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>processed_meat_intake</v>
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.086433159799911</v>
+        <v>1.0695093586575706</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.97921896456946</v>
+        <v>0.9109201832456592</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1.205265651112213</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.838562859743763</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>1.407571295339136</v>
-      </c>
+        <v>1.2557085563529022</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
-        <v>41.47</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>0.083837824241743</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
-        <v>938913</v>
+        <v>647537</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>6956</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="38">
@@ -1593,398 +1587,441 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+        <v>processed_meat_intake</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1.109722458890099</v>
+        <v>1.098230227423644</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1.009977038572974</v>
+        <v>0.9861961589479402</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.219390011363415</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
+        <v>1.2231139195550809</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.8427431092536752</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.4311711590203418</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.03309532537024148</v>
+      </c>
       <c r="J39" s="2" t="n">
-        <v>73024</v>
+        <v>939835</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>297</v>
+        <v>6986</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lutein</v>
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.11</v>
+        <v>1.109722458890099</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.79</v>
+        <v>1.009977038572974</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.57</v>
+        <v>1.219390011363415</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
-        <v>120852</v>
+        <v>73024</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>475</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>dietary_protein_intake</v>
+        <v>lutein</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.117841954220713</v>
+        <v>1.11</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.012983563938329</v>
+        <v>0.79</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.233678059956743</v>
+        <v>1.57</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H41" s="4"/>
       <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
-        <v>585408</v>
+        <v>120852</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2402</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>selenium</v>
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1.129666097028344</v>
+        <v>1.117841954220713</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.700477640283359</v>
+        <v>1.012983563938329</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1.836490637351607</v>
+        <v>1.233678059956743</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
-        <v>34887</v>
+        <v>585408</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>224</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>animal_protein_intake</v>
+        <v>selenium</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1.151654955944369</v>
+        <v>1.129666097028344</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1.038211997081825</v>
+        <v>0.700477640283359</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1.277365814492968</v>
+        <v>1.836490637351607</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H43" s="4"/>
       <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
-        <v>585408</v>
+        <v>34887</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2402</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>tomato</v>
+        <v>animal_protein_intake</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.19945453907786</v>
+        <v>1.151654955944369</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.950107996733684</v>
+        <v>1.038211997081825</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1.518204486493061</v>
+        <v>1.277365814492968</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
-        <v>101683</v>
+        <v>585408</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>774</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>red_meat</v>
+        <v>calcium</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.32154300883515</v>
+        <v>1.1698786201893066</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.111710699877804</v>
+        <v>0.8336013404157353</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1.570980583701342</v>
+        <v>1.6419753520733475</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.781587403506308</v>
+        <v>0.029223708876296984</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.234524144537297</v>
+        <v>46.832385025779665</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>77.01</v>
+        <v>61.22</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.01127626650555</v>
+        <v>0.09782654651999097</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1417360</v>
+        <v>493396</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>6876</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>calcium</v>
+        <v>tomato</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.763833989140762</v>
+        <v>1.19945453907786</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1</v>
+        <v>0.950107996733684</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>3.119550071749652</v>
+        <v>1.518204486493061</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
-        <v>586</v>
+        <v>101683</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>200</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>caffeine</v>
+        <v>red_meat</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2.045114195119933</v>
+        <v>1.32154300883515</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1.149607920243644</v>
+        <v>1.111710699877804</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>3.637955664073244</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="5"/>
+        <v>1.570980583701342</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.781587403506308</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2.234524144537297</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>77.01</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.01127626650555</v>
+      </c>
       <c r="J47" s="2" t="n">
-        <v>104440</v>
+        <v>1417360</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>206</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>pickled_vegetables</v>
+        <v>caffeine</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.217136946095633</v>
+        <v>2.045114195119933</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.357780842990217</v>
+        <v>1.149607920243644</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.482070687809</v>
+        <v>3.637955664073244</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="5"/>
       <c r="J48" s="2" t="n">
-        <v>260</v>
+        <v>104440</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>130</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>vegetable_and_seed_oil_intake</v>
+        <v>pickled_vegetables</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>3.431519625226634</v>
+        <v>3.217136946095633</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1.684722438489189</v>
+        <v>1.357780842990217</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>6.946365883186642</v>
+        <v>7.482070687809</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
       <c r="I49" s="5"/>
       <c r="J49" s="2" t="n">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>eggs</v>
+        <v>vegetable_and_seed_oil_intake</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3.857811292537815</v>
+        <v>3.431519625226634</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2.646928735129925</v>
+        <v>1.684722438489189</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>5.622632665288498</v>
+        <v>6.946365883186642</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H50" s="4"/>
       <c r="I50" s="5"/>
       <c r="J50" s="2" t="n">
-        <v>1995</v>
+        <v>405</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>355</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>soy</v>
+        <v>eggs</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>4.61</v>
+        <v>3.857811292537815</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1.57</v>
+        <v>2.646928735129925</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>13.51</v>
+        <v>5.622632665288498</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I51" s="5"/>
       <c r="J51" s="2" t="n">
-        <v>18244</v>
+        <v>1995</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>61</v>
+        <v>355</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>anti_inflammatory_diet</v>
+        <v>soy</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>5.609539624201962</v>
+        <v>4.61</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1.456957290394739</v>
+        <v>1.57</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>20.449495214599413</v>
+        <v>13.51</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="5"/>
       <c r="J52" s="2" t="n">
+        <v>18244</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>anti_inflammatory_diet</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>5.609539624201962</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1.456957290394739</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>20.449495214599413</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K53" s="2" t="n">
         <v>95</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K52"/>
+  <autoFilter ref="A1:K53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -450,62 +450,86 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="str">
-        <v>Exposure</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>number estimates</v>
-      </c>
-      <c r="C1" s="1" t="str">
-        <v>Pooled RR</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>lower CI RR</v>
-      </c>
-      <c r="E1" s="1" t="str">
-        <v>upper CI RR</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <v>lower PI RR</v>
-      </c>
-      <c r="G1" s="1" t="str">
-        <v>upper PI RR</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>I^2 (%)</v>
-      </c>
-      <c r="I1" s="1" t="str">
-        <v>eggers p-value</v>
-      </c>
-      <c r="J1" s="1" t="str">
-        <v>total N</v>
-      </c>
-      <c r="K1" s="1" t="str">
-        <v>total Cases</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>number estimates</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pooled RR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lower CI RR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>upper CI RR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower PI RR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper PI RR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>I^2 (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>eggers p-value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total N</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>total Cases</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>alpha_linolenic_acid</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>alpha_linolenic_acid</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.260876440489468</v>
+        <v>0.2608764404894685</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.100410276389327</v>
+        <v>0.1004102763893268</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.651034493810665</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
+        <v>0.6510344938106651</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>561</v>
       </c>
@@ -514,25 +538,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.260876440489468</v>
+        <v>0.2608764404894685</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.100410276389327</v>
+        <v>0.1004102763893268</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.651034493810665</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+        <v>0.6510344938106651</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>561</v>
       </c>
@@ -541,25 +567,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.260876440489468</v>
+        <v>0.2608764404894685</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.100410276389327</v>
+        <v>0.1004102763893268</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.651034493810665</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+        <v>0.6510344938106651</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>561</v>
       </c>
@@ -568,25 +596,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>multivitamin</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>multivitamin</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.391083065441434</v>
+        <v>0.3910830654414335</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.240830963155271</v>
+        <v>0.2408309631552709</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.631060054679851</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+        <v>0.6310600546798513</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>667</v>
       </c>
@@ -595,25 +625,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>linoleic_acid</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.431115641055925</v>
+        <v>0.4311156410559245</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.960174367665168</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
+        <v>0.9601743676651679</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>561</v>
       </c>
@@ -622,25 +654,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>omega_6_fatty_acids</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.431115641055925</v>
+        <v>0.4311156410559245</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.960174367665168</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+        <v>0.9601743676651679</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="2" t="n">
         <v>561</v>
       </c>
@@ -649,25 +683,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>olive</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>olive</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.471133641768824</v>
+        <v>0.4711336417688241</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.28091826562668</v>
+        <v>0.2809182656266805</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.780779842907096</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+        <v>0.7807798429070956</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>586</v>
       </c>
@@ -676,25 +712,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>olive_oil_intake</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>olive_oil_intake</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.471133641768824</v>
+        <v>0.4711336417688241</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.28091826562668</v>
+        <v>0.2809182656266805</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.780779842907096</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
+        <v>0.7807798429070956</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>586</v>
       </c>
@@ -703,25 +741,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>vitamin_b3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.561120895100052</v>
+        <v>0.5611208951000519</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.310974157646243</v>
+        <v>0.3109741576462426</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.019907392408769</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>561</v>
       </c>
@@ -730,25 +770,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>vitamin_d</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.581108056842788</v>
+        <v>0.5811080568427878</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.310974157646243</v>
+        <v>0.3109741576462426</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.059711334632446</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="2" t="n">
         <v>561</v>
       </c>
@@ -757,27 +799,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>legumes</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>legumes</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.639799777008446</v>
+        <v>0.6397997770084459</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.43050342469035</v>
+        <v>0.4305034246903502</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.950753928672327</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+        <v>0.9507539286723269</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="4" t="n">
         <v>77.91</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="2" t="n">
         <v>2541</v>
       </c>
@@ -786,27 +830,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>yogurt</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.643585753340495</v>
+        <v>0.6435857533404954</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.249424254265901</v>
+        <v>0.2494242542659014</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1.660634901453039</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
         <v>70.34</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
         <v>101981</v>
       </c>
@@ -815,32 +861,34 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>whole_grain_intake</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>whole_grain_intake</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.722671873564311</v>
+        <v>0.7226718735643111</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.517730729033908</v>
+        <v>0.5177307290339085</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1.008737954989623</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.016586344693104</v>
+        <v>0.01658634469437209</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>31.487024206007852</v>
+        <v>31.48702420360033</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>75.47</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.282267842710602</v>
+        <v>0.2822678427106021</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>219042</v>
@@ -850,32 +898,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>folic_acid</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.731103677210392</v>
+        <v>0.7311036772103915</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.509105507511186</v>
+        <v>0.5091055075111857</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1.049905331889996</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.154279118347241</v>
+        <v>0.1542791183442667</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3.464581549056503</v>
+        <v>3.4645815491233</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>72.21</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.111680789752863</v>
+        <v>0.1116807897528627</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>307597</v>
@@ -885,32 +935,34 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>fermented_foods</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fermented_foods</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.749012205402669</v>
+        <v>0.7490122054026693</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.50242947357177</v>
+        <v>0.5024294735717695</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1.116613004117546</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.199970020367752</v>
+        <v>0.1999700203677981</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.805516961044641</v>
+        <v>2.805516961043995</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>73.37</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.664600832130755</v>
+        <v>0.6646008321307549</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>203999</v>
@@ -920,25 +972,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>non_nutritive_sweetener_intake</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>non_nutritive_sweetener_intake</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.75042643220284</v>
+        <v>0.7504264322028401</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.530566718453295</v>
+        <v>0.5305667184532947</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>1.059855422172594</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
         <v>80388</v>
       </c>
@@ -947,26 +1001,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>vitamin_c</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.750962170993504</v>
+        <v>0.7509621709935039</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.555603704809794</v>
+        <v>0.5556037048097945</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1.014910062303704</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.051104129752821</v>
+        <v>0.05110412975560341</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.035197839997357</v>
+        <v>11.03519783939657</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>26.75</v>
@@ -982,27 +1038,29 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>vitamin_a</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.769203280850767</v>
+        <v>0.7692032808507674</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.392939351855482</v>
+        <v>0.3929393518554822</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.505612812937898</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+        <v>1.505612812937899</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>73.15</v>
-      </c>
-      <c r="I19" s="5"/>
+        <v>73.15000000000001</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
         <v>121519</v>
       </c>
@@ -1011,25 +1069,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_b12</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_b12</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.7708048744499</v>
+        <v>0.7708048744499005</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.611081981756899</v>
+        <v>0.6110819817568988</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0.990044948040641</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>2589</v>
       </c>
@@ -1038,27 +1098,29 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>avocado</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>avocado</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.777322466429106</v>
+        <v>0.7773224664291063</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.595949110875099</v>
+        <v>0.5959491108750986</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1.013794275030678</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
         <v>112328</v>
       </c>
@@ -1067,8 +1129,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>dairy</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>10</v>
@@ -1080,19 +1144,19 @@
         <v>0.6515507423707737</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.0536918026427677</v>
+        <v>1.053691802642768</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0.3820831459958125</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.7966378090761093</v>
+        <v>1.796637809076109</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>78.58</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.13803210241351754</v>
+        <v>0.1380321024135174</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>799763</v>
@@ -1102,25 +1166,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.830320865518684</v>
+        <v>0.8303208655186842</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.67050290986441</v>
+        <v>0.6705029098644103</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>1.029929753803904</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
         <v>101721</v>
       </c>
@@ -1129,27 +1195,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>plant_protein_intake</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.838701849328638</v>
+        <v>0.8387018493286374</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.704829041431359</v>
+        <v>0.7048290414313586</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.998101803857376</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+        <v>0.9981018038573761</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="4" t="n">
         <v>38.28</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1158,27 +1226,29 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.853081662870152</v>
+        <v>0.8530816628701524</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.763608542540667</v>
+        <v>0.7636085425406669</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.952943179381494</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+        <v>0.9529431793814942</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
         <v>676447</v>
       </c>
@@ -1187,23 +1257,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>alcohol</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.859761718188435</v>
+        <v>0.8597617181884347</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.737639541391075</v>
+        <v>0.7376395413910748</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1.002002001334</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.518575557319163</v>
+        <v>0.5185755573191629</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>1.425424321739458</v>
@@ -1212,7 +1284,7 @@
         <v>86.22</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.120413157123371</v>
+        <v>0.1204131571233708</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>881889</v>
@@ -1222,25 +1294,27 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>soluble_dietary_fiber_intake</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>soluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.86027378065949</v>
+        <v>0.8602737806594901</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.680494941324601</v>
+        <v>0.6804949413246006</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1.079803598340883</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>101721</v>
       </c>
@@ -1249,26 +1323,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>vitamin_e</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.860277730007413</v>
+        <v>0.8602777300074131</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.6890785559682</v>
+        <v>0.6890785559681998</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.074010744256656</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.528580435718609</v>
+        <v>0.5285804357154186</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.400123278759961</v>
+        <v>1.400123278768412</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
@@ -1284,26 +1360,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>beta_carotene</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.88232042085284</v>
+        <v>0.8823204208528399</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.707229538705112</v>
+        <v>0.7072295387051121</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.100648993591191</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.450158033189006</v>
+        <v>0.4501580331890583</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.729368949697432</v>
+        <v>1.72936894969723</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>54.04</v>
@@ -1319,25 +1397,27 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>mediterranean_diet</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mediterranean_diet</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.89022260720354</v>
+        <v>0.8902226072035401</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.620535931927757</v>
+        <v>0.6205359319277568</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1.259255513560131</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
         <v>37442</v>
       </c>
@@ -1346,14 +1426,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.946295869852334</v>
+        <v>0.9462958698523343</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0.436660182850176</v>
@@ -1361,12 +1443,12 @@
       <c r="E31" s="3" t="n">
         <v>2.050943641160259</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="4" t="n">
         <v>88.7</v>
       </c>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>648914</v>
       </c>
@@ -1375,23 +1457,25 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>tea</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.961750709146367</v>
+        <v>0.9617507091463667</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7890701910915</v>
+        <v>0.7890701910914995</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1.172337946680718</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.511755210128155</v>
+        <v>0.5117552101281551</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>1.807435289836927</v>
@@ -1400,7 +1484,7 @@
         <v>83.53</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.023983766177595</v>
+        <v>0.02398376617759525</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>580076</v>
@@ -1410,27 +1494,29 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>phosphorus</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>phosphorus</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.974042832922562</v>
+        <v>0.9740428329225616</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.271226774976421</v>
+        <v>0.2712267749764213</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>3.498030164795818</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>82.46</v>
-      </c>
-      <c r="I33" s="5"/>
+        <v>82.45999999999999</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
         <v>1147</v>
       </c>
@@ -1439,8 +1525,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>vitamin_b1</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
@@ -1449,22 +1537,22 @@
         <v>1.026135700809198</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.876078132212251</v>
+        <v>0.8760781322122511</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.201895627523871</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.186121587717069</v>
+        <v>0.1861215877235061</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5.657347379154214</v>
+        <v>5.657347378958566</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>71.67</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.617981208321553</v>
+        <v>0.6179812083215517</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>575001</v>
@@ -1474,8 +1562,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>iron</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1484,15 +1574,15 @@
         <v>1.049880653285851</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.990022507427809</v>
+        <v>0.9900225074278087</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>1.119694504834913</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>481419</v>
       </c>
@@ -1501,8 +1591,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>lycopene</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>2</v>
@@ -1511,17 +1603,17 @@
         <v>1.053375742513365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.865801163613694</v>
+        <v>0.8658011636136935</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.281588084594754</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>222535</v>
       </c>
@@ -1530,27 +1622,29 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.0695093586575706</v>
+        <v>1.069509358657571</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.9109201832456592</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1.2557085563529022</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+        <v>1.255708556352902</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
         <v>647537</v>
       </c>
@@ -1559,25 +1653,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>western_pattern_diet</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>western_pattern_diet</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1.089777005663733</v>
+        <v>1.089777005663734</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.86027378065949</v>
+        <v>0.8602737806594901</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1.378808493040073</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>388077</v>
       </c>
@@ -1586,8 +1682,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>8</v>
@@ -1599,19 +1697,19 @@
         <v>0.9861961589479402</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.2231139195550809</v>
+        <v>1.223113919555081</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.8427431092536752</v>
+        <v>0.8427431092536743</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1.4311711590203418</v>
+        <v>1.431171159020343</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>42.14</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.03309532537024148</v>
+        <v>0.03309532537024146</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>939835</v>
@@ -1621,14 +1719,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.109722458890099</v>
+        <v>1.1097224588901</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1.009977038572974</v>
@@ -1636,10 +1736,10 @@
       <c r="E40" s="3" t="n">
         <v>1.219390011363415</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>73024</v>
       </c>
@@ -1648,8 +1748,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>lutein</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -1663,10 +1765,10 @@
       <c r="E41" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1675,8 +1777,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>2</v>
@@ -1690,12 +1794,12 @@
       <c r="E42" s="3" t="n">
         <v>1.233678059956743</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1704,8 +1808,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>selenium</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1714,15 +1820,15 @@
         <v>1.129666097028344</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.700477640283359</v>
+        <v>0.7004776402833592</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>1.836490637351607</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>34887</v>
       </c>
@@ -1731,8 +1837,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>2</v>
@@ -1746,12 +1854,12 @@
       <c r="E44" s="3" t="n">
         <v>1.277365814492968</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5"/>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="2" t="n">
         <v>585408</v>
       </c>
@@ -1760,26 +1868,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>calcium</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.1698786201893066</v>
+        <v>1.169878620189307</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0.8336013404157353</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1.6419753520733475</v>
+        <v>1.641975352073348</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.029223708876296984</v>
+        <v>0.02922370887848131</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>46.832385025779665</v>
+        <v>46.83238502227918</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>61.22</v>
@@ -1795,8 +1905,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>tomato</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1805,15 +1917,15 @@
         <v>1.19945453907786</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.950107996733684</v>
+        <v>0.9501079967336835</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>1.518204486493061</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>101683</v>
       </c>
@@ -1822,8 +1934,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>red_meat</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>9</v>
@@ -1838,16 +1952,16 @@
         <v>1.570980583701342</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.781587403506308</v>
+        <v>0.7815874035063086</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>2.234524144537297</v>
+        <v>2.234524144537296</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>77.01</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.01127626650555</v>
+        <v>0.01127626650555046</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1417360</v>
@@ -1857,8 +1971,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>caffeine</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>caffeine</t>
+        </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -1872,10 +1988,10 @@
       <c r="E48" s="3" t="n">
         <v>3.637955664073244</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="5"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="2" t="n">
         <v>104440</v>
       </c>
@@ -1884,8 +2000,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>pickled_vegetables</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>pickled_vegetables</t>
+        </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
@@ -1899,10 +2017,10 @@
       <c r="E49" s="3" t="n">
         <v>7.482070687809</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="5"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="2" t="n">
         <v>260</v>
       </c>
@@ -1911,8 +2029,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>vegetable_and_seed_oil_intake</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>vegetable_and_seed_oil_intake</t>
+        </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
@@ -1926,10 +2046,10 @@
       <c r="E50" s="3" t="n">
         <v>6.946365883186642</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="5"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="2" t="n">
         <v>405</v>
       </c>
@@ -1938,8 +2058,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>eggs</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>2</v>
@@ -1953,12 +2075,12 @@
       <c r="E51" s="3" t="n">
         <v>5.622632665288498</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5"/>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="2" t="n">
         <v>1995</v>
       </c>
@@ -1967,8 +2089,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>soy</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>soy</t>
+        </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -1982,10 +2106,10 @@
       <c r="E52" s="3" t="n">
         <v>13.51</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="5"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="2" t="n">
         <v>18244</v>
       </c>
@@ -1994,8 +2118,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>anti_inflammatory_diet</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
@@ -2007,12 +2133,12 @@
         <v>1.456957290394739</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>20.449495214599413</v>
-      </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="5"/>
+        <v>20.44949521459941</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="2" t="n">
         <v>199</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,26 +526,26 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -543,26 +555,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -572,26 +584,26 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -601,26 +613,26 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.3910830654414335</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.2408309631552709</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.6310600546798513</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>667</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>262</v>
       </c>
     </row>
@@ -630,26 +642,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.4311156410559245</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.19070128490511</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.9601743676651679</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -659,26 +671,26 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.4311156410559245</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.19070128490511</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.9601743676651679</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -688,26 +700,26 @@
           <t>olive</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.4711336417688241</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.2809182656266805</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.7807798429070956</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>586</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>200</v>
       </c>
     </row>
@@ -717,26 +729,26 @@
           <t>olive_oil_intake</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.4711336417688241</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.2809182656266805</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.7807798429070956</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>586</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>200</v>
       </c>
     </row>
@@ -746,26 +758,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.5611208951000519</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.3109741576462426</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>1.019907392408769</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -775,26 +787,26 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.5811080568427878</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.3109741576462426</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>1.059711334632446</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -804,28 +816,28 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.6397997770084459</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.4305034246903502</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.9507539286723269</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
         <v>77.91</v>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>2541</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>1268</v>
       </c>
     </row>
@@ -835,28 +847,28 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.6435857533404954</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.2494242542659014</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>1.660634901453039</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
         <v>70.34</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>101981</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>906</v>
       </c>
     </row>
@@ -866,34 +878,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>0.7226718735643111</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.5177307290339085</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>1.008737954989623</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0.01658634469437209</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>31.48702420360033</v>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="F14" s="4" t="n">
+        <v>0.01658634469310387</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>31.48702420600785</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>75.47</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0.2822678427106021</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="6" t="n">
+        <v>0.282267842710602</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>219042</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>1666</v>
       </c>
     </row>
@@ -903,34 +915,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.7311036772103915</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.5091055075111857</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>1.049905331889996</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1542791183442667</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>3.4645815491233</v>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="F15" s="4" t="n">
+        <v>0.1542791183472412</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>3.464581549056503</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="6" t="n">
         <v>0.1116807897528627</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>307597</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>1465</v>
       </c>
     </row>
@@ -940,34 +952,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.7490122054026693</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.5024294735717695</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>1.116613004117546</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0.1999700203677981</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2.805516961043995</v>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0.199970020367752</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2.805516961044641</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>73.37</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0.6646008321307549</v>
-      </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="6" t="n">
+        <v>0.6646008321307553</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>203999</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2474</v>
       </c>
     </row>
@@ -977,26 +989,26 @@
           <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.7504264322028401</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.5305667184532947</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>1.059855422172594</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>80388</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>448</v>
       </c>
     </row>
@@ -1006,34 +1018,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.7509621709935039</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.5556037048097945</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>1.014910062303704</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0.05110412975560341</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.03519783939657</v>
-      </c>
-      <c r="H18" s="4" t="n">
+      <c r="F18" s="4" t="n">
+        <v>0.05110412975282114</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>11.03519783999736</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>26.75</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0.749881599168729</v>
-      </c>
-      <c r="J18" s="2" t="n">
+      <c r="I18" s="6" t="n">
+        <v>0.7498815991687289</v>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>8606</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>902</v>
       </c>
     </row>
@@ -1043,28 +1055,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.7692032808507674</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.3929393518554822</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.505612812937899</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
         <v>73.15000000000001</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>121519</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>737</v>
       </c>
     </row>
@@ -1074,26 +1086,26 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>0.7708048744499005</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.6110819817568988</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.990044948040641</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>2589</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>1171</v>
       </c>
     </row>
@@ -1103,28 +1115,28 @@
           <t>avocado</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.7773224664291063</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.5959491108750986</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.013794275030678</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="n">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
         <v>20.99</v>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="2" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
         <v>112328</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>1165</v>
       </c>
     </row>
@@ -1134,34 +1146,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>0.8285318499048928</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.6515507423707737</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.053691802642768</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="4" t="n">
         <v>0.3820831459958125</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="4" t="n">
         <v>1.796637809076109</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>78.58</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>0.1380321024135174</v>
-      </c>
-      <c r="J22" s="2" t="n">
+      <c r="I22" s="6" t="n">
+        <v>0.1380321024135175</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>799763</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>5469</v>
       </c>
     </row>
@@ -1171,26 +1183,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>0.8303208655186842</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.6705029098644103</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.029929753803904</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="3" t="n">
         <v>101721</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1200,28 +1212,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>0.8387018493286374</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.7048290414313586</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>0.9981018038573761</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
         <v>38.28</v>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>585408</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1231,28 +1243,28 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>0.8530816628701524</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.7636085425406669</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>0.9529431793814942</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
         <v>676447</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>3990</v>
       </c>
     </row>
@@ -1262,34 +1274,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>0.8597617181884347</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.7376395413910748</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.002002001334</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>0.5185755573191629</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="4" t="n">
         <v>1.425424321739458</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>86.22</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0.1204131571233708</v>
-      </c>
-      <c r="J26" s="2" t="n">
+      <c r="I26" s="6" t="n">
+        <v>0.1204131571233709</v>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>881889</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>8536</v>
       </c>
     </row>
@@ -1299,26 +1311,26 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>0.8602737806594901</v>
-      </c>
-      <c r="D27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0.86027378065949</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>0.6804949413246006</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.079803598340883</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>101721</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1328,34 +1340,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.8602777300074131</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.6890785559681998</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.074010744256656</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0.5285804357154186</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>1.400123278768412</v>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="F28" s="4" t="n">
+        <v>0.528580435718609</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1.400123278759961</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I28" s="6" t="n">
         <v>0.616262017938434</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="3" t="n">
         <v>157524</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>1453</v>
       </c>
     </row>
@@ -1365,34 +1377,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>0.8823204208528399</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.7072295387051121</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>1.100648993591191</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>0.4501580331890583</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>1.72936894969723</v>
-      </c>
-      <c r="H29" s="4" t="n">
+      <c r="F29" s="4" t="n">
+        <v>0.4501580331890057</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1.729368949697432</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>54.04</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>0.70006696399279</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="I29" s="6" t="n">
+        <v>0.7000669639927901</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>366541</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>1449</v>
       </c>
     </row>
@@ -1402,26 +1414,26 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="3" t="n">
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>0.8902226072035401</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.6205359319277568</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>1.259255513560131</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="3" t="n">
         <v>37442</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>379</v>
       </c>
     </row>
@@ -1431,28 +1443,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.9462958698523343</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.436660182850176</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>2.050943641160259</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="n">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
         <v>88.7</v>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="2" t="n">
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
         <v>648914</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>3592</v>
       </c>
     </row>
@@ -1462,34 +1474,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>0.9617507091463667</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.7890701910914995</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.172337946680718</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>0.5117552101281551</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="4" t="n">
+        <v>0.5117552101281549</v>
+      </c>
+      <c r="G32" s="4" t="n">
         <v>1.807435289836927</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>83.53</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>0.02398376617759525</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="I32" s="6" t="n">
+        <v>0.02398376617759524</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>580076</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>9039</v>
       </c>
     </row>
@@ -1499,28 +1511,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>0.9740428329225616</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.2712267749764213</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>3.498030164795818</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="n">
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
         <v>82.45999999999999</v>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
         <v>1147</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>522</v>
       </c>
     </row>
@@ -1530,34 +1542,34 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>1.026135700809198</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.8760781322122511</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>1.201895627523871</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0.1861215877235061</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>5.657347378958566</v>
-      </c>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="n">
+        <v>0.1861215877170695</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>5.657347379154213</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>71.67</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>0.6179812083215517</v>
-      </c>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="n">
+        <v>0.6179812083215528</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>575001</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>3737</v>
       </c>
     </row>
@@ -1567,26 +1579,26 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>1.049880653285851</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.9900225074278087</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>1.119694504834913</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>481419</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -1596,28 +1608,28 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>1.053375742513365</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.8658011636136935</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.281588084594754</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>222535</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>1249</v>
       </c>
     </row>
@@ -1627,28 +1639,28 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1.069509358657571</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.9109201832456592</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>1.255708556352902</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>647537</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>1906</v>
       </c>
     </row>
@@ -1658,26 +1670,26 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1.089777005663734</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>0.8602737806594901</v>
-      </c>
-      <c r="E38" s="3" t="n">
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1.089777005663733</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.86027378065949</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>1.378808493040073</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>388077</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>822</v>
       </c>
     </row>
@@ -1687,34 +1699,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>1.098230227423644</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.9861961589479402</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.223113919555081</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>0.8427431092536743</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1.431171159020343</v>
-      </c>
-      <c r="H39" s="4" t="n">
+      <c r="F39" s="4" t="n">
+        <v>0.8427431092536752</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1.431171159020342</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>42.14</v>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>0.03309532537024146</v>
-      </c>
-      <c r="J39" s="2" t="n">
+      <c r="I39" s="6" t="n">
+        <v>0.03309532537024148</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>939835</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>6986</v>
       </c>
     </row>
@@ -1724,26 +1736,26 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1.1097224588901</v>
-      </c>
-      <c r="D40" s="3" t="n">
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1.109722458890099</v>
+      </c>
+      <c r="D40" s="4" t="n">
         <v>1.009977038572974</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.219390011363415</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>73024</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>297</v>
       </c>
     </row>
@@ -1753,26 +1765,26 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="3" t="n">
+      <c r="B41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>475</v>
       </c>
     </row>
@@ -1782,28 +1794,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>1.117841954220713</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>1.012983563938329</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.233678059956743</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="n">
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="3" t="n">
         <v>585408</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1813,26 +1825,26 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="n">
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>1.129666097028344</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>0.7004776402833592</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>1.836490637351607</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>34887</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>224</v>
       </c>
     </row>
@@ -1842,28 +1854,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>1.151654955944369</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>1.038211997081825</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>1.277365814492968</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="n">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
         <v>585408</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1873,34 +1885,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>1.169878620189307</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>0.8336013404157353</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>1.641975352073348</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>0.02922370887848131</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>46.83238502227918</v>
-      </c>
-      <c r="H45" s="4" t="n">
+      <c r="F45" s="4" t="n">
+        <v>0.02922370887629698</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>46.83238502577966</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>61.22</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I45" s="6" t="n">
         <v>0.09782654651999097</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="3" t="n">
         <v>493396</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>1881</v>
       </c>
     </row>
@@ -1910,26 +1922,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>1.19945453907786</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>0.9501079967336835</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1.518204486493061</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>101683</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>774</v>
       </c>
     </row>
@@ -1939,34 +1951,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>1.32154300883515</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>1.111710699877804</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>1.570980583701342</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>0.7815874035063086</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>2.234524144537296</v>
-      </c>
-      <c r="H47" s="4" t="n">
+      <c r="F47" s="4" t="n">
+        <v>0.7815874035063085</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>2.234524144537297</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="I47" s="5" t="n">
-        <v>0.01127626650555046</v>
-      </c>
-      <c r="J47" s="2" t="n">
+      <c r="I47" s="6" t="n">
+        <v>0.01127626650555044</v>
+      </c>
+      <c r="J47" s="3" t="n">
         <v>1417360</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>6876</v>
       </c>
     </row>
@@ -1976,26 +1988,26 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
+      <c r="B48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>2.045114195119933</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>1.149607920243644</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>3.637955664073244</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
         <v>104440</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>206</v>
       </c>
     </row>
@@ -2005,26 +2017,26 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="n">
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="n">
         <v>3.217136946095633</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="4" t="n">
         <v>1.357780842990217</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>7.482070687809</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>130</v>
       </c>
     </row>
@@ -2034,26 +2046,26 @@
           <t>vegetable_and_seed_oil_intake</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="3" t="n">
+      <c r="B50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="n">
         <v>3.431519625226634</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="4" t="n">
         <v>1.684722438489189</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>6.946365883186642</v>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="3" t="n">
         <v>405</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="K50" s="3" t="n">
         <v>113</v>
       </c>
     </row>
@@ -2063,28 +2075,28 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="4" t="n">
         <v>3.857811292537815</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="4" t="n">
         <v>2.646928735129925</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="4" t="n">
         <v>5.622632665288498</v>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="4" t="n">
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="3" t="n">
         <v>1995</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K51" s="3" t="n">
         <v>355</v>
       </c>
     </row>
@@ -2094,26 +2106,26 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="3" t="n">
+      <c r="B52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>4.61</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>13.51</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="3" t="n">
         <v>18244</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K52" s="3" t="n">
         <v>61</v>
       </c>
     </row>
@@ -2123,26 +2135,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="3" t="n">
+      <c r="B53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="n">
         <v>5.609539624201962</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="4" t="n">
         <v>1.456957290394739</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>20.44949521459941</v>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K53" s="3" t="n">
         <v>95</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,26 +514,26 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -555,26 +543,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -584,26 +572,26 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.2608764404894685</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.1004102763893268</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.6510344938106651</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -613,26 +601,26 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.3910830654414335</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.2408309631552709</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.6310600546798513</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -642,26 +630,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.4311156410559245</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.9601743676651679</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -671,26 +659,26 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.4311156410559245</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.19070128490511</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.9601743676651679</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -700,26 +688,26 @@
           <t>olive</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.4711336417688241</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.2809182656266805</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.7807798429070956</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>586</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -729,26 +717,26 @@
           <t>olive_oil_intake</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.4711336417688241</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.2809182656266805</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.7807798429070956</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>586</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -758,26 +746,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.5611208951000519</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.3109741576462426</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>1.019907392408769</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -787,26 +775,26 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.5811080568427878</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.3109741576462426</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.059711334632446</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>561</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>322</v>
       </c>
     </row>
@@ -816,28 +804,28 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.6397997770084459</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.4305034246903502</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.9507539286723269</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
         <v>77.91</v>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>2541</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>1268</v>
       </c>
     </row>
@@ -847,28 +835,28 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>0.6435857533404954</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.2494242542659014</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>1.660634901453039</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
         <v>70.34</v>
       </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>101981</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>906</v>
       </c>
     </row>
@@ -878,34 +866,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>0.7226718735643111</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.5177307290339085</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>1.008737954989623</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.01658634469310387</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>31.48702420600785</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="3" t="n">
+        <v>0.01658634469437209</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>31.48702420360033</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>75.47</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0.282267842710602</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="5" t="n">
+        <v>0.2822678427106021</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>219042</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>1666</v>
       </c>
     </row>
@@ -915,34 +903,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.7311036772103915</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.5091055075111857</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>1.049905331889996</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0.1542791183472412</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>3.464581549056503</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="F15" s="3" t="n">
+        <v>0.1542791183442667</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>3.4645815491233</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.1116807897528627</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="2" t="n">
         <v>307597</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>1465</v>
       </c>
     </row>
@@ -952,34 +940,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.7490122054026693</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.5024294735717695</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>1.116613004117546</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.199970020367752</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2.805516961044641</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0.1999700203677981</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2.805516961043995</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>73.37</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0.6646008321307553</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="5" t="n">
+        <v>0.6646008321307549</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>203999</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2474</v>
       </c>
     </row>
@@ -989,26 +977,26 @@
           <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.7504264322028401</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.5305667184532947</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>1.059855422172594</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>80388</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>448</v>
       </c>
     </row>
@@ -1018,34 +1006,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.7509621709935039</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.5556037048097945</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>1.014910062303704</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05110412975282114</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>11.03519783999736</v>
-      </c>
-      <c r="H18" s="5" t="n">
+      <c r="F18" s="3" t="n">
+        <v>0.05110412975560341</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.03519783939657</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>26.75</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>0.7498815991687289</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="5" t="n">
+        <v>0.749881599168729</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>8606</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>902</v>
       </c>
     </row>
@@ -1055,28 +1043,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.7692032808507674</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.3929393518554822</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.505612812937899</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
         <v>73.15000000000001</v>
       </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>121519</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>737</v>
       </c>
     </row>
@@ -1086,26 +1074,26 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.7708048744499005</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.6110819817568988</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.990044948040641</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>2589</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>1171</v>
       </c>
     </row>
@@ -1115,28 +1103,28 @@
           <t>avocado</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.7773224664291063</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.5959491108750986</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.013794275030678</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="n">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>112328</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>1165</v>
       </c>
     </row>
@@ -1146,34 +1134,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="3" t="n">
         <v>0.8285318499048928</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.6515507423707737</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.053691802642768</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.3820831459958125</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="3" t="n">
         <v>1.796637809076109</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="4" t="n">
         <v>78.58</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>0.1380321024135175</v>
-      </c>
-      <c r="J22" s="3" t="n">
+      <c r="I22" s="5" t="n">
+        <v>0.1380321024135174</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>799763</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>5469</v>
       </c>
     </row>
@@ -1183,26 +1171,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.8303208655186842</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.6705029098644103</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.029929753803904</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="3" t="n">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>101721</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1212,28 +1200,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.8387018493286374</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.7048290414313586</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.9981018038573761</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
         <v>38.28</v>
       </c>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>585408</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1243,28 +1231,28 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.8530816628701524</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.7636085425406669</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>0.9529431793814942</v>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="n">
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>676447</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>3990</v>
       </c>
     </row>
@@ -1274,34 +1262,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="3" t="n">
         <v>0.8597617181884347</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.7376395413910748</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.002002001334</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="3" t="n">
         <v>0.5185755573191629</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="3" t="n">
         <v>1.425424321739458</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="4" t="n">
         <v>86.22</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <v>0.1204131571233709</v>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="I26" s="5" t="n">
+        <v>0.1204131571233708</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>881889</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>8536</v>
       </c>
     </row>
@@ -1311,26 +1299,26 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>0.86027378065949</v>
-      </c>
-      <c r="D27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.8602737806594901</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>0.6804949413246006</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.079803598340883</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>101721</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1340,34 +1328,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.8602777300074131</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.6890785559681998</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.074010744256656</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0.528580435718609</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1.400123278759961</v>
-      </c>
-      <c r="H28" s="5" t="n">
+      <c r="F28" s="3" t="n">
+        <v>0.5285804357154186</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1.400123278768412</v>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="5" t="n">
         <v>0.616262017938434</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" s="2" t="n">
         <v>157524</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>1453</v>
       </c>
     </row>
@@ -1377,34 +1365,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.8823204208528399</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.7072295387051121</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>1.100648993591191</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>0.4501580331890057</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1.729368949697432</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="F29" s="3" t="n">
+        <v>0.4501580331890583</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1.72936894969723</v>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>54.04</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0.7000669639927901</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="n">
+        <v>0.70006696399279</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>366541</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>1449</v>
       </c>
     </row>
@@ -1414,26 +1402,26 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="n">
+      <c r="B30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>0.8902226072035401</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.6205359319277568</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>1.259255513560131</v>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="3" t="n">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
         <v>37442</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>379</v>
       </c>
     </row>
@@ -1443,28 +1431,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.9462958698523343</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.436660182850176</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>2.050943641160259</v>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="n">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
         <v>88.7</v>
       </c>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
         <v>648914</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>3592</v>
       </c>
     </row>
@@ -1474,34 +1462,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>0.9617507091463667</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.7890701910914995</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.172337946680718</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.5117552101281549</v>
-      </c>
-      <c r="G32" s="4" t="n">
+      <c r="F32" s="3" t="n">
+        <v>0.5117552101281551</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>1.807435289836927</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="4" t="n">
         <v>83.53</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>0.02398376617759524</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="I32" s="5" t="n">
+        <v>0.02398376617759525</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>580076</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>9039</v>
       </c>
     </row>
@@ -1511,28 +1499,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>0.9740428329225616</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.2712267749764213</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>3.498030164795818</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
         <v>82.45999999999999</v>
       </c>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>1147</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>522</v>
       </c>
     </row>
@@ -1542,34 +1530,34 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>1.026135700809198</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.8760781322122511</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>1.201895627523871</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.1861215877170695</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>5.657347379154213</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="n">
+        <v>0.1861215877235061</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>5.657347378958566</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>71.67</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>0.6179812083215528</v>
-      </c>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="n">
+        <v>0.6179812083215517</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>575001</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>3737</v>
       </c>
     </row>
@@ -1579,26 +1567,26 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>1.049880653285851</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.9900225074278087</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>1.119694504834913</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>481419</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -1608,28 +1596,28 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="3" t="n">
         <v>1.053375742513365</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.8658011636136935</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.281588084594754</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>222535</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>1249</v>
       </c>
     </row>
@@ -1639,28 +1627,28 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.069509358657571</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.9109201832456592</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>1.255708556352902</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>647537</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>1906</v>
       </c>
     </row>
@@ -1670,26 +1658,26 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1.089777005663733</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0.86027378065949</v>
-      </c>
-      <c r="E38" s="4" t="n">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1.089777005663734</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0.8602737806594901</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>1.378808493040073</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>388077</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>822</v>
       </c>
     </row>
@@ -1699,34 +1687,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.098230227423644</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.9861961589479402</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.223113919555081</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>0.8427431092536752</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>1.431171159020342</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="F39" s="3" t="n">
+        <v>0.8427431092536743</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.431171159020343</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>42.14</v>
       </c>
-      <c r="I39" s="6" t="n">
-        <v>0.03309532537024148</v>
-      </c>
-      <c r="J39" s="3" t="n">
+      <c r="I39" s="5" t="n">
+        <v>0.03309532537024146</v>
+      </c>
+      <c r="J39" s="2" t="n">
         <v>939835</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>6986</v>
       </c>
     </row>
@@ -1736,26 +1724,26 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>1.109722458890099</v>
-      </c>
-      <c r="D40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1.1097224588901</v>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>1.009977038572974</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.219390011363415</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>73024</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>297</v>
       </c>
     </row>
@@ -1765,26 +1753,26 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="n">
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="3" t="n">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>475</v>
       </c>
     </row>
@@ -1794,28 +1782,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>1.117841954220713</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.012983563938329</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.233678059956743</v>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="n">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>585408</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1825,26 +1813,26 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1.129666097028344</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.7004776402833592</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>1.836490637351607</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>34887</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>224</v>
       </c>
     </row>
@@ -1854,28 +1842,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="3" t="n">
         <v>1.151654955944369</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>1.038211997081825</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>1.277365814492968</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="n">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>585408</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>2402</v>
       </c>
     </row>
@@ -1885,34 +1873,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="3" t="n">
         <v>1.169878620189307</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.8336013404157353</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>1.641975352073348</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>0.02922370887629698</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>46.83238502577966</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="F45" s="3" t="n">
+        <v>0.02922370887848131</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>46.83238502227918</v>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>61.22</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="5" t="n">
         <v>0.09782654651999097</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="J45" s="2" t="n">
         <v>493396</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>1881</v>
       </c>
     </row>
@@ -1922,26 +1910,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1.19945453907786</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.9501079967336835</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>1.518204486493061</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>101683</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>774</v>
       </c>
     </row>
@@ -1951,34 +1939,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>1.32154300883515</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>1.111710699877804</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.570980583701342</v>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>0.7815874035063085</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>2.234524144537297</v>
-      </c>
-      <c r="H47" s="5" t="n">
+      <c r="F47" s="3" t="n">
+        <v>0.7815874035063086</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2.234524144537296</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="I47" s="6" t="n">
-        <v>0.01127626650555044</v>
-      </c>
-      <c r="J47" s="3" t="n">
+      <c r="I47" s="5" t="n">
+        <v>0.01127626650555046</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>1417360</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>6876</v>
       </c>
     </row>
@@ -1988,26 +1976,26 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="n">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>2.045114195119933</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="3" t="n">
         <v>1.149607920243644</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>3.637955664073244</v>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="3" t="n">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>104440</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>206</v>
       </c>
     </row>
@@ -2017,26 +2005,26 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="n">
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>3.217136946095633</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="3" t="n">
         <v>1.357780842990217</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>7.482070687809</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>130</v>
       </c>
     </row>
@@ -2046,26 +2034,26 @@
           <t>vegetable_and_seed_oil_intake</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="n">
+      <c r="B50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>3.431519625226634</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="3" t="n">
         <v>1.684722438489189</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="3" t="n">
         <v>6.946365883186642</v>
       </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="3" t="n">
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>113</v>
       </c>
     </row>
@@ -2075,28 +2063,28 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="3" t="n">
         <v>3.857811292537815</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="3" t="n">
         <v>2.646928735129925</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="3" t="n">
         <v>5.622632665288498</v>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="5" t="n">
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="3" t="n">
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
         <v>1995</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>355</v>
       </c>
     </row>
@@ -2106,26 +2094,26 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4" t="n">
+      <c r="B52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>4.61</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="3" t="n">
         <v>13.51</v>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="3" t="n">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
         <v>18244</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>61</v>
       </c>
     </row>
@@ -2135,26 +2123,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4" t="n">
+      <c r="B53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>5.609539624201962</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="3" t="n">
         <v>1.456957290394739</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="3" t="n">
         <v>20.44949521459941</v>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="3" t="n">
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>95</v>
       </c>
     </row>
